--- a/ttl_long/AdHoc_Net_7.xlsx
+++ b/ttl_long/AdHoc_Net_7.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>248</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>169</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>275</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>45</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>126</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>189</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>187</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>304</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>208</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>389</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>136</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>381</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>368</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>442</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>258</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>562</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>513</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>685</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>161</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>560</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>353</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>612</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>68</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>708</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>251</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>809</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>295</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>730</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>836</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>106</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1147</t>
+          <t>911</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>328</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>860</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>83</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>998</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>261</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>890</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>350</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>939</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>98</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1172</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>111</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1056</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>278</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1456</t>
+          <t>1104</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1574</t>
+          <t>1150</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,182 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>234</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>1176</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1249</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1294</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1338</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1362</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1521</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1448</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1568</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1559</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1538</t>
         </is>
       </c>
     </row>
@@ -990,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,7 +1215,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1067,7 +1237,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1111,7 +1281,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1133,7 +1303,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1155,7 +1325,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1172,12 +1342,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1199,7 +1369,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1221,7 +1391,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1243,7 +1413,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1265,7 +1435,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1287,7 +1457,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1304,12 +1474,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1331,7 +1501,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1353,7 +1523,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1375,7 +1545,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1397,7 +1567,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1419,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1441,7 +1611,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1463,7 +1633,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1485,7 +1655,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1502,12 +1672,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1529,7 +1699,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1551,7 +1721,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1573,7 +1743,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1617,7 +1787,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1634,12 +1804,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1656,12 +1826,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1678,12 +1848,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1700,7 +1870,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1727,7 +1897,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1744,12 +1914,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1766,12 +1936,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1788,12 +1958,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1815,7 +1985,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1832,12 +2002,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1854,12 +2024,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1876,12 +2046,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1898,12 +2068,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1925,7 +2095,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1947,7 +2117,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1969,7 +2139,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1991,7 +2161,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2008,12 +2178,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2030,12 +2200,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2057,7 +2227,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2079,7 +2249,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2096,12 +2266,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2123,7 +2293,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2140,12 +2310,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2162,12 +2332,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2184,12 +2354,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2206,12 +2376,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2228,12 +2398,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2250,12 +2420,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2272,12 +2442,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2294,12 +2464,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2316,7 +2486,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2338,12 +2508,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2360,12 +2530,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2382,12 +2552,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2404,12 +2574,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2426,12 +2596,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2448,7 +2618,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2470,12 +2640,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2492,12 +2662,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2514,12 +2684,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2536,12 +2706,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2558,12 +2728,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2580,12 +2750,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2602,12 +2772,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2624,12 +2794,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2646,12 +2816,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2668,12 +2838,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2690,12 +2860,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2712,12 +2882,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2734,12 +2904,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2756,12 +2926,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2778,12 +2948,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2800,12 +2970,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2822,20 +2992,856 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -2874,7 +3880,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -2884,7 +3890,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -2910,7 +3916,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>jamm_powe</t>
+          <t>jamm_power</t>
         </is>
       </c>
       <c r="B6" t="n">

--- a/ttl_long/AdHoc_Net_7.xlsx
+++ b/ttl_long/AdHoc_Net_7.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>93</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>85</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>278</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>308</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>203</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>162</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>142</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>385</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>114</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>291</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>146</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>326</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>279</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>323</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>93</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>326</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>384</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>403</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>525</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>56</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>551</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>484</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>95</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>640</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>160</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>628</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>641</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>113</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>797</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>270</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>682</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>387</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>728</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>936</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>89</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>933</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>312</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>842</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>930</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>226</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>1007</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>1014</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1075</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>261</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1149</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1146</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>113</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1218</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>84</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>1297</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>290</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>1246</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1301</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>235</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1299</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1387</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>109</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1442</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>277</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1535</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>387</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1496</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>57</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1568</t>
+          <t>1631</t>
         </is>
       </c>
     </row>
@@ -1123,29 +1123,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>181</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1559</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1538</t>
+          <t>1581</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D122"/>
+  <dimension ref="A1:D114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1193,7 +1176,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1215,7 +1198,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1237,7 +1220,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1281,7 +1264,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1303,7 +1286,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1325,7 +1308,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1369,7 +1352,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1391,7 +1374,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1413,7 +1396,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1430,12 +1413,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1474,12 +1457,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1496,12 +1479,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1545,7 +1528,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,12 +1545,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1572,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1606,12 +1589,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1633,7 +1616,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1655,7 +1638,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1672,12 +1655,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1699,7 +1682,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1721,7 +1704,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1738,12 +1721,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1782,12 +1765,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1826,12 +1809,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1853,7 +1836,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1870,12 +1853,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1892,12 +1875,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1936,12 +1919,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1958,12 +1941,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1980,12 +1963,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2002,12 +1985,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2024,12 +2007,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2051,7 +2034,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2068,7 +2051,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2090,12 +2073,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2112,12 +2095,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2134,12 +2117,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2156,12 +2139,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2178,12 +2161,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2200,12 +2183,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2222,12 +2205,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2244,12 +2227,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2266,12 +2249,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2288,12 +2271,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2310,12 +2293,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2332,12 +2315,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2354,7 +2337,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2376,12 +2359,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2398,12 +2381,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2420,12 +2403,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2442,12 +2425,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2464,12 +2447,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2486,12 +2469,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2508,12 +2491,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2530,12 +2513,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2552,7 +2535,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2574,12 +2557,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2596,12 +2579,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2618,12 +2601,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2640,12 +2623,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2662,12 +2645,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2684,12 +2667,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2706,12 +2689,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2728,12 +2711,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2750,12 +2733,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2772,12 +2755,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2794,7 +2777,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2816,12 +2799,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2838,12 +2821,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2860,12 +2843,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2882,12 +2865,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2904,12 +2887,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2926,12 +2909,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2948,12 +2931,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2970,12 +2953,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2992,12 +2975,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3014,12 +2997,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3036,12 +3019,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3058,12 +3041,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3080,12 +3063,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3102,12 +3085,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3124,12 +3107,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3146,12 +3129,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3168,12 +3151,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3190,12 +3173,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3212,12 +3195,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3234,12 +3217,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3256,12 +3239,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3278,12 +3261,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3300,12 +3283,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3322,12 +3305,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3344,12 +3327,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>38</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3366,12 +3349,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3388,12 +3371,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3410,12 +3393,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3432,12 +3415,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3454,12 +3437,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3476,12 +3459,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
           <t>34</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3498,12 +3481,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3520,12 +3503,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3542,12 +3525,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3564,12 +3547,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3586,12 +3569,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>33</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3608,12 +3591,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3630,12 +3613,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>39</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3652,12 +3635,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3666,182 +3649,6 @@
         </is>
       </c>
       <c r="D114" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -3880,7 +3687,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -3910,7 +3717,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6">

--- a/ttl_long/AdHoc_Net_7.xlsx
+++ b/ttl_long/AdHoc_Net_7.xlsx
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>185</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>44</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>324</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>90</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>56</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>289</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>93</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>106</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>272</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>213</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>201</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>342</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>217</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>301</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>85</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>431</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>410</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>63</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>563</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>208</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>479</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>307</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>507</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>96</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>623</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>191</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>552</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>604</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>759</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>144</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>792</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>291</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>789</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>56</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>890</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>148</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>859</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>323</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>861</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>1000</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>72</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>927</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>342</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>995</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>97</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1048</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>66</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1187</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1161</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>102</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1284</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>156</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1326</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1215</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1405</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>129</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1378</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>279</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1354</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>68</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1541</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>185</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1515</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>296</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1532</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1599</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>149</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1581</t>
+          <t>1537</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D114"/>
+  <dimension ref="A1:D125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1501,12 +1501,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1743,12 +1743,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1787,12 +1787,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1809,12 +1809,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1853,12 +1853,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1919,12 +1919,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1941,12 +1941,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1963,12 +1963,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1985,12 +1985,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2029,12 +2029,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2051,12 +2051,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2073,12 +2073,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2117,12 +2117,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2139,12 +2139,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2161,7 +2161,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2183,12 +2183,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2205,12 +2205,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2227,12 +2227,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2249,12 +2249,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2293,12 +2293,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2315,12 +2315,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2337,12 +2337,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2359,12 +2359,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2381,12 +2381,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2403,7 +2403,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2425,12 +2425,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2447,12 +2447,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2469,7 +2469,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2491,12 +2491,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2513,12 +2513,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2535,12 +2535,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2557,12 +2557,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2579,12 +2579,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2601,12 +2601,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2623,12 +2623,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2645,12 +2645,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2667,12 +2667,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2689,12 +2689,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2711,12 +2711,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2733,12 +2733,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2755,12 +2755,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2777,12 +2777,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2799,12 +2799,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2821,12 +2821,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2843,12 +2843,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2865,12 +2865,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2887,12 +2887,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2909,12 +2909,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2931,12 +2931,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2953,12 +2953,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2975,12 +2975,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2997,12 +2997,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3019,7 +3019,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3063,12 +3063,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3085,12 +3085,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3107,12 +3107,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3129,12 +3129,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3151,7 +3151,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3173,12 +3173,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3195,12 +3195,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3217,12 +3217,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3239,12 +3239,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3261,12 +3261,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3283,12 +3283,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3305,12 +3305,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3327,12 +3327,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3349,12 +3349,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
           <t>34</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3371,12 +3371,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3393,12 +3393,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3415,12 +3415,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3437,12 +3437,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3459,12 +3459,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3481,12 +3481,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3503,12 +3503,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3525,7 +3525,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3547,12 +3547,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3569,12 +3569,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3591,12 +3591,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3613,12 +3613,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3635,20 +3635,262 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -3687,7 +3929,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -3697,7 +3939,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
